--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486739_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486739_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7075</v>
+        <v>3.9751</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7823</v>
+        <v>4.0995</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.1245</v>
       </c>
       <c r="G2" t="n">
         <v>0.6679</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0606</v>
+        <v>0.2069</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5796</v>
+        <v>-0.2624</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5189</v>
+        <v>0.4693</v>
       </c>
       <c r="V2" t="n">
         <v>2.521</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. PÉREZ PEREZ</t>
+          <t>M. VILLANUEVA CUBELO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1951</v>
+        <v>1.0662</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4545</v>
+        <v>1.401</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2594</v>
+        <v>-0.3348</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3505</v>
+        <v>2.0012</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.883</v>
+        <v>0.1859</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2335</v>
+        <v>1.8153</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1241</v>
+        <v>3.5539</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0488</v>
+        <v>1.0829</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0753</v>
+        <v>2.471</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7736</v>
+        <v>-1.5527</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9318</v>
+        <v>-0.897</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1582</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9308</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7553</v>
+        <v>-0.0276</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3304</v>
+        <v>-0.1795</v>
       </c>
       <c r="U3" t="n">
-        <v>0.425</v>
+        <v>0.152</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.8415</v>
+        <v>-0.3282</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.8415</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. VILLANUEVA CUBELO</t>
+          <t>A. PÉREZ PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7794</v>
+        <v>0.9774</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1389</v>
+        <v>1.8891</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3596</v>
+        <v>-0.9117</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0012</v>
+        <v>0.3505</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1859</v>
+        <v>-1.883</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8153</v>
+        <v>2.2335</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5539</v>
+        <v>2.1241</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0829</v>
+        <v>0.0488</v>
       </c>
       <c r="L4" t="n">
-        <v>2.471</v>
+        <v>2.0753</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5527</v>
+        <v>-1.7736</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.897</v>
+        <v>-1.9318</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.1582</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5792</v>
+        <v>1.9308</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3515</v>
+        <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3144</v>
+        <v>0.5376</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4416</v>
+        <v>-0.235</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1272</v>
+        <v>0.7726</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3282</v>
+        <v>-1.8415</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0426</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1558</v>
+        <v>0.1116</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0811</v>
+        <v>-1.0259</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2368</v>
+        <v>1.1375</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7159</v>
@@ -844,13 +844,13 @@
         <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.1379</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4966</v>
+        <v>-0.4415</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4029</v>
+        <v>0.3036</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BIURRUN SANTAMARIA</t>
+          <t>G. COMACHIO COACHMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6546</v>
+        <v>-0.7047</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4834</v>
+        <v>-0.1489</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1379</v>
+        <v>-0.5558</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3243</v>
+        <v>-1.3289</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3516</v>
+        <v>-0.0968</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-1.2321</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3868</v>
+        <v>0.3547</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1796</v>
+        <v>0.2485</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2072</v>
+        <v>0.1063</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7112</v>
+        <v>-1.6837</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.828</v>
+        <v>-0.3453</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8832</v>
+        <v>-1.3384</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5446</v>
+        <v>0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3169</v>
+        <v>-0.3862</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7779</v>
+        <v>-0.0206</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4135</v>
+        <v>-0.1174</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3644</v>
+        <v>0.0968</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4365</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4365</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. COMACHIO COACHMAN</t>
+          <t>A. BIURRUN SANTAMARIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1419</v>
+        <v>-1.1083</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3626</v>
+        <v>0.2283</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7793</v>
+        <v>-1.3366</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3289</v>
+        <v>-0.3243</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0968</v>
+        <v>0.3516</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2321</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3547</v>
+        <v>2.3868</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2485</v>
+        <v>1.1796</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1063</v>
+        <v>1.2072</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6837</v>
+        <v>-2.7112</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3453</v>
+        <v>-0.828</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3384</v>
+        <v>-1.8832</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3862</v>
+        <v>-2.3169</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4579</v>
+        <v>0.3242</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3312</v>
+        <v>0.1584</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1267</v>
+        <v>0.1658</v>
       </c>
       <c r="V7" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.4365</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.4365</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4259</v>
+        <v>-2.513</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8569</v>
+        <v>-2.5466</v>
       </c>
       <c r="F8" t="n">
-        <v>0.431</v>
+        <v>0.0336</v>
       </c>
       <c r="G8" t="n">
         <v>-5.2094</v>
@@ -1078,13 +1078,13 @@
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3973</v>
+        <v>0.3103</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8554</v>
+        <v>-0.5451</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2527</v>
+        <v>0.8554</v>
       </c>
       <c r="V8" t="n">
         <v>1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8102</v>
+        <v>-3.8391</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0361</v>
+        <v>-2.1395</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7741</v>
+        <v>-1.6996</v>
       </c>
       <c r="G9" t="n">
         <v>-2.485</v>
@@ -1156,13 +1156,13 @@
         <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6011</v>
+        <v>0.5722</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0272</v>
+        <v>-0.0762</v>
       </c>
       <c r="U9" t="n">
-        <v>0.574</v>
+        <v>0.6484</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7333</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. BERGERON</t>
+          <t>J. FERMIN DE LUNA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.59</v>
+        <v>-5.6664</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1064</v>
+        <v>-5.2381</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.4836</v>
+        <v>-0.4283</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0656</v>
+        <v>-3.4666</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0068</v>
+        <v>-3.4825</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0588</v>
+        <v>0.0158</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2454</v>
+        <v>-1.9624</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0409</v>
+        <v>-1.9647</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2863</v>
+        <v>0.0023</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.311</v>
+        <v>-1.5043</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9659</v>
+        <v>-1.5178</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3451</v>
+        <v>0.0135</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5446</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7613</v>
+        <v>0.1171</v>
       </c>
       <c r="T10" t="n">
-        <v>0.579</v>
+        <v>-0.3796</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1823</v>
+        <v>0.4967</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.741</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. FERMIN DE LUNA</t>
+          <t>G. BERGERON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0264</v>
+        <v>-6.0478</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5484</v>
+        <v>-1.4649</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.478</v>
+        <v>-4.5829</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4666</v>
+        <v>-2.0656</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.4825</v>
+        <v>-2.0068</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0158</v>
+        <v>-0.0588</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9624</v>
+        <v>0.2454</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9647</v>
+        <v>-1.0409</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0023</v>
+        <v>1.2863</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5043</v>
+        <v>-2.311</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5178</v>
+        <v>-0.9659</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0135</v>
+        <v>-1.3451</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3169</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2428</v>
+        <v>0.3034</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6898</v>
+        <v>0.2205</v>
       </c>
       <c r="U11" t="n">
-        <v>0.447</v>
+        <v>0.083</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.741</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.7305</v>
+        <v>-7.2409</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8279</v>
+        <v>-6.4624</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9026</v>
+        <v>-0.7784</v>
       </c>
       <c r="G12" t="n">
         <v>-5.0775</v>
@@ -1390,13 +1390,13 @@
         <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1933</v>
+        <v>0.2964</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8555</v>
+        <v>-0.4901</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6622</v>
+        <v>0.7864</v>
       </c>
       <c r="V12" t="n">
         <v>0.4365</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.5417</v>
+        <v>-20.9899</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.9603</v>
+        <v>-11.4084</v>
       </c>
       <c r="F13" t="n">
         <v>-9.5815</v>
@@ -1456,7 +1456,7 @@
         <v>-14.4885</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.5904</v>
+        <v>-6.590400000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-3.861499999999999</v>
@@ -1468,13 +1468,13 @@
         <v>12.5501</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9301</v>
+        <v>2.482</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.8996</v>
+        <v>-2.3479</v>
       </c>
       <c r="U13" t="n">
-        <v>4.829899999999999</v>
+        <v>4.83</v>
       </c>
       <c r="V13" t="n">
         <v>-1.9567</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.164</v>
+        <v>8.3279</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3847</v>
+        <v>4.7984</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7793</v>
+        <v>3.5296</v>
       </c>
       <c r="G14" t="n">
         <v>6.8259</v>
@@ -1546,13 +1546,13 @@
         <v>2.7031</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.357</v>
+        <v>-0.1931</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0485</v>
+        <v>-0.6348</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3085</v>
+        <v>0.4417</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0426</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6168</v>
+        <v>4.8555</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3189</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2979</v>
+        <v>4.8468</v>
       </c>
       <c r="G15" t="n">
         <v>3.2665</v>
@@ -1624,13 +1624,13 @@
         <v>2.3169</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2869</v>
+        <v>-0.0482</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5245</v>
+        <v>-0.8348</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2376</v>
+        <v>0.7866</v>
       </c>
       <c r="V15" t="n">
         <v>0.2856</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5122</v>
+        <v>4.0719</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4868</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0254</v>
+        <v>3.4817</v>
       </c>
       <c r="G16" t="n">
         <v>3.8727</v>
@@ -1702,13 +1702,13 @@
         <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>0.806</v>
+        <v>0.3657</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8277</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6337</v>
+        <v>1.09</v>
       </c>
       <c r="V16" t="n">
         <v>1.1851</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6985</v>
+        <v>3.4268</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4487</v>
+        <v>2.1384</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2498</v>
+        <v>1.2884</v>
       </c>
       <c r="G17" t="n">
         <v>4.1121</v>
@@ -1780,13 +1780,13 @@
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5131</v>
+        <v>0.2414</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3038</v>
+        <v>-0.6141</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8169</v>
+        <v>0.8555</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3129</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RELAÑO LOPEZ</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9298</v>
+        <v>3.1428</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8824</v>
+        <v>4.4389</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0474</v>
+        <v>-1.2961</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5988</v>
+        <v>2.5593</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9447</v>
+        <v>2.3038</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3459</v>
+        <v>0.2555</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5928</v>
+        <v>4.9876</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7383</v>
+        <v>2.5799</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8545</v>
+        <v>2.4077</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.994</v>
+        <v>-2.4283</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2065</v>
+        <v>-0.2761</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2005</v>
+        <v>-2.1522</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.9308</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.9654</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.9654</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.9308</v>
-      </c>
       <c r="S18" t="n">
-        <v>0.138</v>
+        <v>-0.007</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0273</v>
+        <v>-0.1312</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1107</v>
+        <v>0.1242</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2277</v>
+        <v>1.5559</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2277</v>
+        <v>1.5133</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>A. BARBEITO RUIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4326</v>
+        <v>3.1118</v>
       </c>
       <c r="E19" t="n">
-        <v>4.1287</v>
+        <v>1.0472</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.696</v>
+        <v>2.0646</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5593</v>
+        <v>1.4126</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3038</v>
+        <v>1.6274</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2555</v>
+        <v>-0.2148</v>
       </c>
       <c r="J19" t="n">
-        <v>4.9876</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5799</v>
+        <v>0.7316</v>
       </c>
       <c r="L19" t="n">
-        <v>2.4077</v>
+        <v>0.1651</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4283</v>
+        <v>0.5159</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2761</v>
+        <v>0.8958</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1522</v>
+        <v>-0.3799</v>
       </c>
       <c r="P19" t="n">
+        <v>1.5446</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.9308</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.9654</v>
+        <v>2.51</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.131</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4415</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2757</v>
+        <v>0.552</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5559</v>
+        <v>0.2856</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5133</v>
+        <v>1.7989</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0426</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BARBEITO RUIZ</t>
+          <t>A. RELAÑO LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.0402</v>
+        <v>3.0125</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7369</v>
+        <v>1.6756</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3033</v>
+        <v>1.337</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4126</v>
+        <v>0.5988</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6274</v>
+        <v>0.9447</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2148</v>
+        <v>-0.3459</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8967000000000001</v>
+        <v>1.5928</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7316</v>
+        <v>0.7383</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1651</v>
+        <v>0.8545</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5159</v>
+        <v>-0.994</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8958</v>
+        <v>0.2065</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3799</v>
+        <v>-1.2005</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>2.51</v>
+        <v>1.9308</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2026</v>
+        <v>0.2206</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9933</v>
+        <v>-0.1795</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2093</v>
+        <v>0.4002</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7989</v>
+        <v>1.2277</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Í. MATEO CASTAÑO</t>
+          <t>R. TERRATS MADRID</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1905</v>
+        <v>0.1379</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2247</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0342</v>
+        <v>0.1379</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7275</v>
+        <v>0.1379</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2687</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9962</v>
+        <v>0.1379</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6734</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2001</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5266999999999999</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4009</v>
+        <v>0.1379</v>
       </c>
       <c r="N21" t="n">
-        <v>0.06859999999999999</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4695</v>
+        <v>0.1379</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7377</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7377</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.408</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5512</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1432</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. TERRATS MADRID</t>
+          <t>Í. MATEO CASTAÑO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1379</v>
+        <v>0.0444</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.6041</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1379</v>
+        <v>-0.5597</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1379</v>
+        <v>-0.7275</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1.2687</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1379</v>
+        <v>-1.9962</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.6734</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.2001</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1379</v>
+        <v>-1.4009</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1379</v>
+        <v>-1.4695</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.2619</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.0693</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.3312</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4245</v>
+        <v>-1.1335</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0393</v>
+        <v>0.1427</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4638</v>
+        <v>-1.2762</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2093</v>
@@ -2248,13 +2248,13 @@
         <v>0.1931</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4082</v>
+        <v>-0.1172</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1655</v>
+        <v>-0.0621</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2427</v>
+        <v>-0.0551</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7636</v>
+        <v>-1.7595</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9107</v>
+        <v>-2.8072</v>
       </c>
       <c r="F24" t="n">
-        <v>1.147</v>
+        <v>1.0477</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5391</v>
@@ -2326,13 +2326,13 @@
         <v>0.5792</v>
       </c>
       <c r="S24" t="n">
-        <v>0.127</v>
+        <v>0.1311</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4966</v>
+        <v>-0.3932</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6236</v>
+        <v>0.5243</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9927</v>
+        <v>-2.939</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1589</v>
+        <v>-3.0555</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1662</v>
+        <v>0.1165</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6563</v>
@@ -2404,13 +2404,13 @@
         <v>0.5792</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0497</v>
+        <v>0.1035</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.607</v>
+        <v>-0.5036</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6567</v>
+        <v>0.6071</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>21.5417</v>
+        <v>24.2995</v>
       </c>
       <c r="E26" t="n">
         <v>9.581500000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>11.9602</v>
+        <v>14.7182</v>
       </c>
       <c r="G26" t="n">
         <v>17.6536</v>
@@ -2452,7 +2452,7 @@
         <v>16.8964</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7571999999999997</v>
+        <v>0.7571999999999988</v>
       </c>
       <c r="J26" t="n">
         <v>21.0786</v>
@@ -2461,7 +2461,7 @@
         <v>14.4884</v>
       </c>
       <c r="L26" t="n">
-        <v>6.590399999999999</v>
+        <v>6.590400000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-3.4251</v>
@@ -2470,7 +2470,7 @@
         <v>2.4083</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.833299999999999</v>
+        <v>-5.833300000000001</v>
       </c>
       <c r="P26" t="n">
         <v>3.861600000000001</v>
@@ -2482,16 +2482,16 @@
         <v>16.4115</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.9301</v>
+        <v>0.8277000000000001</v>
       </c>
       <c r="T26" t="n">
         <v>-4.8299</v>
       </c>
       <c r="U26" t="n">
-        <v>2.899799999999999</v>
+        <v>5.657699999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>1.9567</v>
+        <v>1.956700000000001</v>
       </c>
       <c r="W26" t="n">
         <v>5.8828</v>
